--- a/Parametrit/Jäljellejäämiskertoimet/Jäljellejäämiskerroin.xlsx
+++ b/Parametrit/Jäljellejäämiskertoimet/Jäljellejäämiskerroin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanga\Documents\Vaestoennuste-main\Parametrit\Jäljellejäämiskertoimet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D520B43-1F94-4388-9077-06ACF812482F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CF1C93-5F21-4570-862C-96F2F854B1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50800" yWindow="4920" windowWidth="24350" windowHeight="7520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Taul1" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>jj0</t>
   </si>
@@ -352,6 +352,15 @@
   </si>
   <si>
     <t>Kerrostalo</t>
+  </si>
+  <si>
+    <t>Pienkerrostalo</t>
+  </si>
+  <si>
+    <t>OK-talo-haja-asutus</t>
+  </si>
+  <si>
+    <t>Hoivakoti</t>
   </si>
 </sst>
 </file>
@@ -411,9 +420,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -721,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8925825-D9F6-441D-8714-98872F20496C}">
-  <dimension ref="A1:CX5"/>
+  <dimension ref="A1:CX8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.6328125" customWidth="1"/>
@@ -729,1542 +737,2466 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:102" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BL1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BM1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BN1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BO1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BP1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BR1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BS1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BT1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BU1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BV1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BW1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BX1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BY1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CA1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CB1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CC1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CD1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CE1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CF1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CG1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CH1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CI1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CK1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CL1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CM1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CN1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CO1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CP1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CR1" s="2" t="s">
+      <c r="CR1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CS1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CT1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CU1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CV1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CW1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CX1" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:102" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>1.25</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>1.25</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>1.25</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>1.1889205084349999</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>1.1206959932585279</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <v>1.0312764243475234</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <v>1.0470144721784416</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="3">
         <v>1.0252111374343276</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="3">
         <v>1.0158825703078325</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>0.99754043202865872</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="3">
         <v>0.99615957883364437</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="3">
         <v>0.97685656321898762</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="3">
         <v>0.96039856462072815</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="3">
         <v>0.96846207848766475</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="3">
         <v>0.95498319542299226</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="3">
         <v>0.94337556574899339</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="3">
         <v>0.96744839262155014</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="3">
         <v>0.92769338530705725</v>
       </c>
-      <c r="U2" s="4">
+      <c r="U2" s="3">
         <v>0.86727206296066028</v>
       </c>
-      <c r="V2" s="4">
+      <c r="V2" s="3">
         <v>0.82472017699640998</v>
       </c>
-      <c r="W2" s="4">
+      <c r="W2" s="3">
         <v>0.76894002397572891</v>
       </c>
-      <c r="X2" s="4">
+      <c r="X2" s="3">
         <v>0.66380679626800254</v>
       </c>
-      <c r="Y2" s="4">
+      <c r="Y2" s="3">
         <v>0.65305631166753941</v>
       </c>
-      <c r="Z2" s="4">
+      <c r="Z2" s="3">
         <v>0.6871152299415384</v>
       </c>
-      <c r="AA2" s="4">
+      <c r="AA2" s="3">
         <v>0.71859481887835241</v>
       </c>
-      <c r="AB2" s="4">
+      <c r="AB2" s="3">
         <v>0.74790223711309056</v>
       </c>
-      <c r="AC2" s="4">
+      <c r="AC2" s="3">
         <v>0.79091784715273028</v>
       </c>
-      <c r="AD2" s="4">
+      <c r="AD2" s="3">
         <v>0.81121586681599944</v>
       </c>
-      <c r="AE2" s="4">
+      <c r="AE2" s="3">
         <v>0.94913668647105376</v>
       </c>
-      <c r="AF2" s="4">
+      <c r="AF2" s="3">
         <v>1.0870575061261083</v>
       </c>
-      <c r="AG2" s="4">
+      <c r="AG2" s="3">
         <v>1.0964746257051343</v>
       </c>
-      <c r="AH2" s="4">
+      <c r="AH2" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AI2" s="4">
+      <c r="AI2" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AJ2" s="4">
+      <c r="AJ2" s="3">
         <v>1.0781097574837049</v>
       </c>
-      <c r="AK2" s="4">
+      <c r="AK2" s="3">
         <v>1.0409106501042227</v>
       </c>
-      <c r="AL2" s="4">
+      <c r="AL2" s="3">
         <v>1.0608518171660311</v>
       </c>
-      <c r="AM2" s="4">
+      <c r="AM2" s="3">
         <v>1.0807929842278394</v>
       </c>
-      <c r="AN2" s="4">
+      <c r="AN2" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AO2" s="4">
+      <c r="AO2" s="3">
         <v>1.0464763732622839</v>
       </c>
-      <c r="AP2" s="4">
+      <c r="AP2" s="3">
         <v>0.99221859523491995</v>
       </c>
-      <c r="AQ2" s="4">
+      <c r="AQ2" s="3">
         <v>1.01501463678607</v>
       </c>
-      <c r="AR2" s="4">
+      <c r="AR2" s="3">
         <v>1.0378106783372201</v>
       </c>
-      <c r="AS2" s="4">
+      <c r="AS2" s="3">
         <v>1.06060671988837</v>
       </c>
-      <c r="AT2" s="4">
+      <c r="AT2" s="3">
         <v>1.0057961170209109</v>
       </c>
-      <c r="AU2" s="4">
+      <c r="AU2" s="3">
         <v>0.95098551415345178</v>
       </c>
-      <c r="AV2" s="4">
+      <c r="AV2" s="3">
         <v>0.96222260153095573</v>
       </c>
-      <c r="AW2" s="4">
+      <c r="AW2" s="3">
         <v>0.97345968890845957</v>
       </c>
-      <c r="AX2" s="4">
+      <c r="AX2" s="3">
         <v>0.98469677628596364</v>
       </c>
-      <c r="AY2" s="4">
+      <c r="AY2" s="3">
         <v>0.99037643241413353</v>
       </c>
-      <c r="AZ2" s="4">
+      <c r="AZ2" s="3">
         <v>0.99605608854230321</v>
       </c>
-      <c r="BA2" s="4">
+      <c r="BA2" s="3">
         <v>0.98736234926232114</v>
       </c>
-      <c r="BB2" s="4">
+      <c r="BB2" s="3">
         <v>0.97866860998233918</v>
       </c>
-      <c r="BC2" s="4">
+      <c r="BC2" s="3">
         <v>0.96997487070235722</v>
       </c>
-      <c r="BD2" s="4">
+      <c r="BD2" s="3">
         <v>0.96398692483800841</v>
       </c>
-      <c r="BE2" s="4">
+      <c r="BE2" s="3">
         <v>0.9579989789736596</v>
       </c>
-      <c r="BF2" s="4">
+      <c r="BF2" s="3">
         <v>0.95893696143103158</v>
       </c>
-      <c r="BG2" s="4">
+      <c r="BG2" s="3">
         <v>0.95987494388840366</v>
       </c>
-      <c r="BH2" s="4">
+      <c r="BH2" s="3">
         <v>0.96081292634577564</v>
       </c>
-      <c r="BI2" s="4">
+      <c r="BI2" s="3">
         <v>0.93768707847620991</v>
       </c>
-      <c r="BJ2" s="4">
+      <c r="BJ2" s="3">
         <v>0.91456123060664429</v>
       </c>
-      <c r="BK2" s="4">
+      <c r="BK2" s="3">
         <v>0.91099708676497237</v>
       </c>
-      <c r="BL2" s="4">
+      <c r="BL2" s="3">
         <v>0.90743294292330057</v>
       </c>
-      <c r="BM2" s="4">
+      <c r="BM2" s="3">
         <v>0.90386879908162854</v>
       </c>
-      <c r="BN2" s="4">
+      <c r="BN2" s="3">
         <v>0.96274866013250016</v>
       </c>
-      <c r="BO2" s="4">
+      <c r="BO2" s="3">
         <v>1.021628521183372</v>
       </c>
-      <c r="BP2" s="4">
+      <c r="BP2" s="3">
         <v>1.014419014122248</v>
       </c>
-      <c r="BQ2" s="4">
+      <c r="BQ2" s="3">
         <v>1.007209507061124</v>
       </c>
-      <c r="BR2" s="4">
-        <v>1</v>
-      </c>
-      <c r="BS2" s="4">
-        <v>1</v>
-      </c>
-      <c r="BT2" s="4">
-        <v>1</v>
-      </c>
-      <c r="BU2" s="4">
-        <v>1</v>
-      </c>
-      <c r="BV2" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW2" s="4">
-        <v>1</v>
-      </c>
-      <c r="BX2" s="4">
-        <v>1</v>
-      </c>
-      <c r="BY2" s="4">
-        <v>1</v>
-      </c>
-      <c r="BZ2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CA2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CB2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CC2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CD2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CE2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CF2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CG2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CH2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CI2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CJ2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CK2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CL2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CM2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CN2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CO2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CP2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CQ2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CR2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CS2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CT2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CU2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CV2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CW2" s="4">
-        <v>1</v>
-      </c>
-      <c r="CX2" s="4">
+      <c r="BR2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BT2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BU2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BZ2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CA2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CC2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CD2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CE2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CF2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CG2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CH2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CI2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CJ2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CK2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CM2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CO2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CP2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CQ2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CS2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CT2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CW2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CX2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>1.25</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>1.25</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>1.25</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>1.1496680967307049</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>1.0606359344049605</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <v>0.98596280933347447</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>0.96470143211538095</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="3">
         <v>0.95802260959710706</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="3">
         <v>0.97526071686859006</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="3">
         <v>0.97124367623771679</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="3">
         <v>0.9694203480837249</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="3">
         <v>0.98079937376828996</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="3">
         <v>0.99943182461855007</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="3">
         <v>0.98096884232002246</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="Q3" s="3">
         <v>0.98579840377185801</v>
       </c>
-      <c r="R3" s="4">
+      <c r="R3" s="3">
         <v>0.97591489501871675</v>
       </c>
-      <c r="S3" s="4">
+      <c r="S3" s="3">
         <v>0.96024539095077921</v>
       </c>
-      <c r="T3" s="4">
+      <c r="T3" s="3">
         <v>0.93446115292793297</v>
       </c>
-      <c r="U3" s="4">
+      <c r="U3" s="3">
         <v>0.87368531421227869</v>
       </c>
-      <c r="V3" s="4">
+      <c r="V3" s="3">
         <v>0.82644101823519889</v>
       </c>
-      <c r="W3" s="4">
+      <c r="W3" s="3">
         <v>0.7941525643461832</v>
       </c>
-      <c r="X3" s="4">
+      <c r="X3" s="3">
         <v>0.78986807467418019</v>
       </c>
-      <c r="Y3" s="4">
+      <c r="Y3" s="3">
         <v>0.80109058801951938</v>
       </c>
-      <c r="Z3" s="4">
+      <c r="Z3" s="3">
         <v>1.0100793286068894</v>
       </c>
-      <c r="AA3" s="4">
+      <c r="AA3" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AB3" s="4">
+      <c r="AB3" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AC3" s="4">
+      <c r="AC3" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AD3" s="4">
+      <c r="AD3" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AE3" s="4">
+      <c r="AE3" s="3">
         <v>1.0931947966527076</v>
       </c>
-      <c r="AF3" s="4">
+      <c r="AF3" s="3">
         <v>1.0999019523019438</v>
       </c>
-      <c r="AG3" s="4">
+      <c r="AG3" s="3">
         <v>1.0949416443920184</v>
       </c>
-      <c r="AH3" s="4">
+      <c r="AH3" s="3">
         <v>1.0899813364820932</v>
       </c>
-      <c r="AI3" s="4">
+      <c r="AI3" s="3">
         <v>1.0850210285721682</v>
       </c>
-      <c r="AJ3" s="4">
+      <c r="AJ3" s="3">
         <v>1.0433451880798503</v>
       </c>
-      <c r="AK3" s="4">
+      <c r="AK3" s="3">
         <v>1.0016693475875322</v>
       </c>
-      <c r="AL3" s="4">
+      <c r="AL3" s="3">
         <v>1.0168405599216386</v>
       </c>
-      <c r="AM3" s="4">
+      <c r="AM3" s="3">
         <v>1.0320117722557445</v>
       </c>
-      <c r="AN3" s="4">
+      <c r="AN3" s="3">
         <v>1.0471829845898508</v>
       </c>
-      <c r="AO3" s="4">
+      <c r="AO3" s="3">
         <v>1.009371736403377</v>
       </c>
-      <c r="AP3" s="4">
+      <c r="AP3" s="3">
         <v>0.97156048821690355</v>
       </c>
-      <c r="AQ3" s="4">
+      <c r="AQ3" s="3">
         <v>0.98807311392696595</v>
       </c>
-      <c r="AR3" s="4">
+      <c r="AR3" s="3">
         <v>1.0045857396370284</v>
       </c>
-      <c r="AS3" s="4">
+      <c r="AS3" s="3">
         <v>1.0210983653470909</v>
       </c>
-      <c r="AT3" s="4">
+      <c r="AT3" s="3">
         <v>0.99705001362251444</v>
       </c>
-      <c r="AU3" s="4">
+      <c r="AU3" s="3">
         <v>0.97300166189793802</v>
       </c>
-      <c r="AV3" s="4">
+      <c r="AV3" s="3">
         <v>0.96123987334691796</v>
       </c>
-      <c r="AW3" s="4">
+      <c r="AW3" s="3">
         <v>0.94947808479589801</v>
       </c>
-      <c r="AX3" s="4">
+      <c r="AX3" s="3">
         <v>0.93771629624487807</v>
       </c>
-      <c r="AY3" s="4">
+      <c r="AY3" s="3">
         <v>0.95641493139347988</v>
       </c>
-      <c r="AZ3" s="4">
+      <c r="AZ3" s="3">
         <v>0.9751135665420817</v>
       </c>
-      <c r="BA3" s="4">
+      <c r="BA3" s="3">
         <v>0.97810491026112967</v>
       </c>
-      <c r="BB3" s="4">
+      <c r="BB3" s="3">
         <v>0.98109625398017763</v>
       </c>
-      <c r="BC3" s="4">
+      <c r="BC3" s="3">
         <v>0.9840875976992256</v>
       </c>
-      <c r="BD3" s="4">
+      <c r="BD3" s="3">
         <v>0.97902463758992231</v>
       </c>
-      <c r="BE3" s="4">
+      <c r="BE3" s="3">
         <v>0.9739616774806189</v>
       </c>
-      <c r="BF3" s="4">
+      <c r="BF3" s="3">
         <v>0.98216286977828682</v>
       </c>
-      <c r="BG3" s="4">
+      <c r="BG3" s="3">
         <v>0.99036406207595484</v>
       </c>
-      <c r="BH3" s="4">
+      <c r="BH3" s="3">
         <v>0.99856525437362298</v>
       </c>
-      <c r="BI3" s="4">
+      <c r="BI3" s="3">
         <v>0.98425894097760391</v>
       </c>
-      <c r="BJ3" s="4">
+      <c r="BJ3" s="3">
         <v>0.96995262758158529</v>
       </c>
-      <c r="BK3" s="4">
+      <c r="BK3" s="3">
         <v>0.95250302802180653</v>
       </c>
-      <c r="BL3" s="4">
+      <c r="BL3" s="3">
         <v>0.9350534284620281</v>
       </c>
-      <c r="BM3" s="4">
+      <c r="BM3" s="3">
         <v>0.91760382890224945</v>
       </c>
-      <c r="BN3" s="4">
+      <c r="BN3" s="3">
         <v>0.95514324099567172</v>
       </c>
-      <c r="BO3" s="4">
+      <c r="BO3" s="3">
         <v>0.9926826530890942</v>
       </c>
-      <c r="BP3" s="4">
+      <c r="BP3" s="3">
         <v>0.99512176872606284</v>
       </c>
-      <c r="BQ3" s="4">
+      <c r="BQ3" s="3">
         <v>0.99756088436303147</v>
       </c>
-      <c r="BR3" s="4">
-        <v>1</v>
-      </c>
-      <c r="BS3" s="4">
-        <v>1</v>
-      </c>
-      <c r="BT3" s="4">
-        <v>1</v>
-      </c>
-      <c r="BU3" s="4">
-        <v>1</v>
-      </c>
-      <c r="BV3" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW3" s="4">
-        <v>1</v>
-      </c>
-      <c r="BX3" s="4">
-        <v>1</v>
-      </c>
-      <c r="BY3" s="4">
-        <v>1</v>
-      </c>
-      <c r="BZ3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CA3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CB3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CC3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CD3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CE3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CF3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CG3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CH3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CI3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CJ3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CK3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CL3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CM3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CN3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CO3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CP3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CQ3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CR3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CS3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CT3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CU3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CV3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CW3" s="4">
-        <v>1</v>
-      </c>
-      <c r="CX3" s="4">
+      <c r="BR3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BT3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BU3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BZ3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CA3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CC3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CD3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CE3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CF3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CG3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CH3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CI3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CJ3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CK3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CM3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CO3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CP3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CQ3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CS3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CT3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CW3" s="3">
+        <v>1</v>
+      </c>
+      <c r="CX3" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>1.05</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>1.05</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>1.0253807580151726</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>0.98607184419644422</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>0.95466537814279862</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>0.92381417087727158</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>0.92244672292394969</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>0.93367501647666185</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="3">
         <v>0.95429061397065529</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>0.96551761053102614</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="3">
         <v>0.96886518542140188</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="3">
         <v>0.9790984970606782</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="3">
         <v>0.97804854476606717</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="3">
         <v>0.97946632599547601</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="3">
         <v>0.96711778091258382</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4" s="3">
         <v>1.002931945504749</v>
       </c>
-      <c r="S4" s="4">
+      <c r="S4" s="3">
         <v>1.0203025966975912</v>
       </c>
-      <c r="T4" s="4">
+      <c r="T4" s="3">
         <v>1.058609836702777</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="V4" s="4">
+      <c r="V4" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="W4" s="4">
+      <c r="W4" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="X4" s="4">
+      <c r="X4" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y4" s="4">
+      <c r="Y4" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="Z4" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AA4" s="4">
+      <c r="AA4" s="3">
         <v>1.0898880827597162</v>
       </c>
-      <c r="AB4" s="4">
+      <c r="AB4" s="3">
         <v>1.0603250032747462</v>
       </c>
-      <c r="AC4" s="4">
+      <c r="AC4" s="3">
         <v>1.0493911280146104</v>
       </c>
-      <c r="AD4" s="4">
+      <c r="AD4" s="3">
         <v>1.0256336601044906</v>
       </c>
-      <c r="AE4" s="4">
+      <c r="AE4" s="3">
         <v>0.99733328056388104</v>
       </c>
-      <c r="AF4" s="4">
+      <c r="AF4" s="3">
         <v>0.97665049132156345</v>
       </c>
-      <c r="AG4" s="4">
+      <c r="AG4" s="3">
         <v>0.98236355359864513</v>
       </c>
-      <c r="AH4" s="4">
+      <c r="AH4" s="3">
         <v>0.98807661587572659</v>
       </c>
-      <c r="AI4" s="4">
+      <c r="AI4" s="3">
         <v>0.99378967815280816</v>
       </c>
-      <c r="AJ4" s="4">
+      <c r="AJ4" s="3">
         <v>0.97880768148415687</v>
       </c>
-      <c r="AK4" s="4">
+      <c r="AK4" s="3">
         <v>0.96382568481550535</v>
       </c>
-      <c r="AL4" s="4">
+      <c r="AL4" s="3">
         <v>0.96801501996424977</v>
       </c>
-      <c r="AM4" s="4">
+      <c r="AM4" s="3">
         <v>0.97220435511299375</v>
       </c>
-      <c r="AN4" s="4">
+      <c r="AN4" s="3">
         <v>0.97639369026173795</v>
       </c>
-      <c r="AO4" s="4">
+      <c r="AO4" s="3">
         <v>0.96374918115148545</v>
       </c>
-      <c r="AP4" s="4">
+      <c r="AP4" s="3">
         <v>0.95110467204123272</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="AQ4" s="3">
         <v>0.95686354851294264</v>
       </c>
-      <c r="AR4" s="4">
+      <c r="AR4" s="3">
         <v>0.96262242498465278</v>
       </c>
-      <c r="AS4" s="4">
+      <c r="AS4" s="3">
         <v>0.96838130145636292</v>
       </c>
-      <c r="AT4" s="4">
+      <c r="AT4" s="3">
         <v>0.97130687648770819</v>
       </c>
-      <c r="AU4" s="4">
+      <c r="AU4" s="3">
         <v>0.97423245151905369</v>
       </c>
-      <c r="AV4" s="4">
+      <c r="AV4" s="3">
         <v>0.96999243274593783</v>
       </c>
-      <c r="AW4" s="4">
+      <c r="AW4" s="3">
         <v>0.96575241397282174</v>
       </c>
-      <c r="AX4" s="4">
+      <c r="AX4" s="3">
         <v>0.96151239519970555</v>
       </c>
-      <c r="AY4" s="4">
+      <c r="AY4" s="3">
         <v>0.99605793909747575</v>
       </c>
-      <c r="AZ4" s="4">
+      <c r="AZ4" s="3">
         <v>1.0306034829952462</v>
       </c>
-      <c r="BA4" s="4">
+      <c r="BA4" s="3">
         <v>1.0190239551890197</v>
       </c>
-      <c r="BB4" s="4">
+      <c r="BB4" s="3">
         <v>1.0074444273827936</v>
       </c>
-      <c r="BC4" s="4">
+      <c r="BC4" s="3">
         <v>0.99586489957656732</v>
       </c>
-      <c r="BD4" s="4">
+      <c r="BD4" s="3">
         <v>0.98691573513830677</v>
       </c>
-      <c r="BE4" s="4">
+      <c r="BE4" s="3">
         <v>0.97796657070004667</v>
       </c>
-      <c r="BF4" s="4">
+      <c r="BF4" s="3">
         <v>0.98879143894568688</v>
       </c>
-      <c r="BG4" s="4">
+      <c r="BG4" s="3">
         <v>0.99961630719132688</v>
       </c>
-      <c r="BH4" s="4">
+      <c r="BH4" s="3">
         <v>1.0104411754369671</v>
       </c>
-      <c r="BI4" s="4">
+      <c r="BI4" s="3">
         <v>1.0012453153335852</v>
       </c>
-      <c r="BJ4" s="4">
+      <c r="BJ4" s="3">
         <v>0.99204945523020316</v>
       </c>
-      <c r="BK4" s="4">
+      <c r="BK4" s="3">
         <v>0.99477434712489321</v>
       </c>
-      <c r="BL4" s="4">
+      <c r="BL4" s="3">
         <v>0.99749923901958337</v>
       </c>
-      <c r="BM4" s="4">
+      <c r="BM4" s="3">
         <v>1.0002241309142732</v>
       </c>
-      <c r="BN4" s="4">
+      <c r="BN4" s="3">
         <v>1.0094823448773158</v>
       </c>
-      <c r="BO4" s="4">
+      <c r="BO4" s="3">
         <v>1.018740558840358</v>
       </c>
-      <c r="BP4" s="4">
+      <c r="BP4" s="3">
         <v>1.0124937058935721</v>
       </c>
-      <c r="BQ4" s="4">
+      <c r="BQ4" s="3">
         <v>1.0062468529467861</v>
       </c>
-      <c r="BR4" s="4">
-        <v>1</v>
-      </c>
-      <c r="BS4" s="4">
-        <v>1</v>
-      </c>
-      <c r="BT4" s="4">
-        <v>1</v>
-      </c>
-      <c r="BU4" s="4">
-        <v>1</v>
-      </c>
-      <c r="BV4" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW4" s="4">
-        <v>1</v>
-      </c>
-      <c r="BX4" s="4">
-        <v>1</v>
-      </c>
-      <c r="BY4" s="4">
-        <v>1</v>
-      </c>
-      <c r="BZ4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CA4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CB4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CC4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CD4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CE4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CF4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CG4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CH4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CI4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CJ4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CK4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CL4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CM4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CN4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CO4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CP4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CQ4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CR4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CS4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CT4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CU4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CV4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CW4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CX4" s="4">
+      <c r="BR4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BT4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BU4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BZ4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CA4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CC4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CE4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CF4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CG4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CH4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CI4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CJ4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CK4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CM4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CO4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CP4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CQ4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CS4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CT4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CW4" s="3">
+        <v>1</v>
+      </c>
+      <c r="CX4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>0.97952001483352003</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>0.97952001483352003</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>0.97540326354912921</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>0.95461826773660774</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>0.93759970296988693</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <v>0.96078472300524909</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>1.0145562165118258</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>1.0086436136920858</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>1.0116373178502474</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>1.0379475500672943</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="3">
         <v>1.0149999999999999</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="3">
         <v>1.0035570113374315</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="3">
         <v>0.99822271669434637</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="3">
         <v>1.0141385054110685</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="3">
         <v>1.0671417247412005</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="3">
         <v>1.0874919383395505</v>
       </c>
-      <c r="S5" s="4">
+      <c r="S5" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="3">
         <v>1.2</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5" s="3">
         <v>1.3</v>
       </c>
-      <c r="V5" s="4">
+      <c r="V5" s="3">
         <v>1.5</v>
       </c>
-      <c r="W5" s="4">
+      <c r="W5" s="3">
         <v>1.5</v>
       </c>
-      <c r="X5" s="4">
+      <c r="X5" s="3">
         <v>1.4</v>
       </c>
-      <c r="Y5" s="4">
+      <c r="Y5" s="3">
         <v>1.2</v>
       </c>
-      <c r="Z5" s="4">
+      <c r="Z5" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AA5" s="4">
+      <c r="AA5" s="3">
         <v>1.0792118117396481</v>
       </c>
-      <c r="AB5" s="4">
+      <c r="AB5" s="3">
         <v>1.0431086587829479</v>
       </c>
-      <c r="AC5" s="4">
+      <c r="AC5" s="3">
         <v>1.0305303918597581</v>
       </c>
-      <c r="AD5" s="4">
+      <c r="AD5" s="3">
         <v>1.02960910091903</v>
       </c>
-      <c r="AE5" s="4">
+      <c r="AE5" s="3">
         <v>0.97552556202355523</v>
       </c>
-      <c r="AF5" s="4">
+      <c r="AF5" s="3">
         <v>0.93040475925384636</v>
       </c>
-      <c r="AG5" s="4">
+      <c r="AG5" s="3">
         <v>0.94136721120234623</v>
       </c>
-      <c r="AH5" s="4">
+      <c r="AH5" s="3">
         <v>0.95232966315084633</v>
       </c>
-      <c r="AI5" s="4">
+      <c r="AI5" s="3">
         <v>0.96329211509934642</v>
       </c>
-      <c r="AJ5" s="4">
+      <c r="AJ5" s="3">
         <v>0.95413598979464564</v>
       </c>
-      <c r="AK5" s="4">
+      <c r="AK5" s="3">
         <v>0.94497986448994487</v>
       </c>
-      <c r="AL5" s="4">
+      <c r="AL5" s="3">
         <v>0.9346289884039567</v>
       </c>
-      <c r="AM5" s="4">
+      <c r="AM5" s="3">
         <v>0.92427811231796875</v>
       </c>
-      <c r="AN5" s="4">
+      <c r="AN5" s="3">
         <v>0.91392723623198058</v>
       </c>
-      <c r="AO5" s="4">
+      <c r="AO5" s="3">
         <v>0.92917358972250841</v>
       </c>
-      <c r="AP5" s="4">
+      <c r="AP5" s="3">
         <v>0.94441994321303613</v>
       </c>
-      <c r="AQ5" s="4">
+      <c r="AQ5" s="3">
         <v>0.96753887769936797</v>
       </c>
-      <c r="AR5" s="4">
+      <c r="AR5" s="3">
         <v>0.99065781218570004</v>
       </c>
-      <c r="AS5" s="4">
+      <c r="AS5" s="3">
         <v>1.013776746672032</v>
       </c>
-      <c r="AT5" s="4">
+      <c r="AT5" s="3">
         <v>1.0341979024404673</v>
       </c>
-      <c r="AU5" s="4">
+      <c r="AU5" s="3">
         <v>1.0546190582089023</v>
       </c>
-      <c r="AV5" s="4">
+      <c r="AV5" s="3">
         <v>1.0401889062093603</v>
       </c>
-      <c r="AW5" s="4">
+      <c r="AW5" s="3">
         <v>1.0257587542098183</v>
       </c>
-      <c r="AX5" s="4">
+      <c r="AX5" s="3">
         <v>1.0113286022102765</v>
       </c>
-      <c r="AY5" s="4">
+      <c r="AY5" s="3">
         <v>1.0326642454114474</v>
       </c>
-      <c r="AZ5" s="4">
+      <c r="AZ5" s="3">
         <v>1.0539998886126181</v>
       </c>
-      <c r="BA5" s="4">
+      <c r="BA5" s="3">
         <v>1.0447328356255499</v>
       </c>
-      <c r="BB5" s="4">
+      <c r="BB5" s="3">
         <v>1.0354657826384819</v>
       </c>
-      <c r="BC5" s="4">
+      <c r="BC5" s="3">
         <v>1.0261987296514139</v>
       </c>
-      <c r="BD5" s="4">
+      <c r="BD5" s="3">
         <v>1.0130950774484</v>
       </c>
-      <c r="BE5" s="4">
+      <c r="BE5" s="3">
         <v>0.99999142524538631</v>
       </c>
-      <c r="BF5" s="4">
+      <c r="BF5" s="3">
         <v>1.0167060876249021</v>
       </c>
-      <c r="BG5" s="4">
+      <c r="BG5" s="3">
         <v>1.0334207500044179</v>
       </c>
-      <c r="BH5" s="4">
+      <c r="BH5" s="3">
         <v>1.0334207500044179</v>
       </c>
-      <c r="BI5" s="4">
+      <c r="BI5" s="3">
         <v>1.0334207500044179</v>
       </c>
-      <c r="BJ5" s="4">
+      <c r="BJ5" s="3">
         <v>1.0334207500044179</v>
       </c>
-      <c r="BK5" s="4">
+      <c r="BK5" s="3">
         <v>1.0103056275505184</v>
       </c>
-      <c r="BL5" s="4">
+      <c r="BL5" s="3">
         <v>0.98323319568007794</v>
       </c>
-      <c r="BM5" s="4">
+      <c r="BM5" s="3">
         <v>0.95616076380963722</v>
       </c>
-      <c r="BN5" s="4">
+      <c r="BN5" s="3">
         <v>0.9635555349254028</v>
       </c>
-      <c r="BO5" s="4">
+      <c r="BO5" s="3">
         <v>0.97095030604116828</v>
       </c>
-      <c r="BP5" s="4">
+      <c r="BP5" s="3">
         <v>0.98063353736077874</v>
       </c>
-      <c r="BQ5" s="4">
+      <c r="BQ5" s="3">
         <v>0.99031676868038931</v>
       </c>
-      <c r="BR5" s="4">
-        <v>1</v>
-      </c>
-      <c r="BS5" s="4">
-        <v>1</v>
-      </c>
-      <c r="BT5" s="4">
-        <v>1</v>
-      </c>
-      <c r="BU5" s="4">
-        <v>1</v>
-      </c>
-      <c r="BV5" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW5" s="4">
-        <v>1</v>
-      </c>
-      <c r="BX5" s="4">
-        <v>1</v>
-      </c>
-      <c r="BY5" s="4">
-        <v>1</v>
-      </c>
-      <c r="BZ5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CA5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CB5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CC5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CD5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CE5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CF5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CG5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CH5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CI5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CJ5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CK5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CL5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CM5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CN5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CO5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CP5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CQ5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CR5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CS5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CT5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CU5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CV5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CW5" s="4">
-        <v>1</v>
-      </c>
-      <c r="CX5" s="4">
+      <c r="BR5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BT5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BU5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BZ5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CA5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CC5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CE5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CF5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CG5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CH5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CI5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CJ5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CK5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CM5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CO5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CP5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CQ5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CS5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CT5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CW5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CX5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.97952001483352003</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.97952001483352003</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.97540326354912921</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.95461826773660774</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.93759970296988693</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.96078472300524909</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1.0145562165118258</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1.0086436136920858</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1.0116373178502474</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1.0379475500672943</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="N6" s="3">
+        <v>1.0035570113374315</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.99822271669434637</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1.0141385054110685</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>1.0671417247412005</v>
+      </c>
+      <c r="R6" s="3">
+        <v>1.0874919383395505</v>
+      </c>
+      <c r="S6" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="V6" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="W6" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>1.0792118117396481</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>1.0431086587829479</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1.0305303918597581</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>1.02960910091903</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>0.97552556202355523</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>0.93040475925384636</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>0.94136721120234623</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>0.95232966315084633</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>0.96329211509934642</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>0.95413598979464564</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>0.94497986448994487</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>0.9346289884039567</v>
+      </c>
+      <c r="AM6" s="3">
+        <v>0.92427811231796875</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>0.91392723623198058</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>0.92917358972250841</v>
+      </c>
+      <c r="AP6" s="3">
+        <v>0.94441994321303613</v>
+      </c>
+      <c r="AQ6" s="3">
+        <v>0.96753887769936797</v>
+      </c>
+      <c r="AR6" s="3">
+        <v>0.99065781218570004</v>
+      </c>
+      <c r="AS6" s="3">
+        <v>1.013776746672032</v>
+      </c>
+      <c r="AT6" s="3">
+        <v>1.0341979024404673</v>
+      </c>
+      <c r="AU6" s="3">
+        <v>1.0546190582089023</v>
+      </c>
+      <c r="AV6" s="3">
+        <v>1.0401889062093603</v>
+      </c>
+      <c r="AW6" s="3">
+        <v>1.0257587542098183</v>
+      </c>
+      <c r="AX6" s="3">
+        <v>1.0113286022102765</v>
+      </c>
+      <c r="AY6" s="3">
+        <v>1.0326642454114474</v>
+      </c>
+      <c r="AZ6" s="3">
+        <v>1.0539998886126181</v>
+      </c>
+      <c r="BA6" s="3">
+        <v>1.0447328356255499</v>
+      </c>
+      <c r="BB6" s="3">
+        <v>1.0354657826384819</v>
+      </c>
+      <c r="BC6" s="3">
+        <v>1.0261987296514139</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>1.0130950774484</v>
+      </c>
+      <c r="BE6" s="3">
+        <v>0.99999142524538631</v>
+      </c>
+      <c r="BF6" s="3">
+        <v>1.0167060876249021</v>
+      </c>
+      <c r="BG6" s="3">
+        <v>1.0334207500044179</v>
+      </c>
+      <c r="BH6" s="3">
+        <v>1.0334207500044179</v>
+      </c>
+      <c r="BI6" s="3">
+        <v>1.0334207500044179</v>
+      </c>
+      <c r="BJ6" s="3">
+        <v>1.0334207500044179</v>
+      </c>
+      <c r="BK6" s="3">
+        <v>1.0103056275505184</v>
+      </c>
+      <c r="BL6" s="3">
+        <v>0.98323319568007794</v>
+      </c>
+      <c r="BM6" s="3">
+        <v>0.95616076380963722</v>
+      </c>
+      <c r="BN6" s="3">
+        <v>0.9635555349254028</v>
+      </c>
+      <c r="BO6" s="3">
+        <v>0.97095030604116828</v>
+      </c>
+      <c r="BP6" s="3">
+        <v>0.98063353736077874</v>
+      </c>
+      <c r="BQ6" s="3">
+        <v>0.99031676868038931</v>
+      </c>
+      <c r="BR6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BT6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BU6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BZ6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CA6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CE6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CF6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CG6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CH6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CI6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CJ6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CK6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CM6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CO6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CP6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CQ6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CS6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CT6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CW6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CX6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1</v>
+      </c>
+      <c r="O7" s="3">
+        <v>1</v>
+      </c>
+      <c r="P7" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3">
+        <v>1</v>
+      </c>
+      <c r="S7" s="3">
+        <v>1</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1</v>
+      </c>
+      <c r="U7" s="3">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3">
+        <v>1</v>
+      </c>
+      <c r="W7" s="3">
+        <v>1</v>
+      </c>
+      <c r="X7" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BC7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BF7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BG7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BH7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BI7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BJ7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BK7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BL7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BM7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BN7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BQ7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BR7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BT7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BU7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BZ7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CA7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CC7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CE7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CF7" s="3">
+        <v>0.76894002397572891</v>
+      </c>
+      <c r="CG7" s="3">
+        <v>0.66380679626800254</v>
+      </c>
+      <c r="CH7" s="3">
+        <v>0.65305631166753941</v>
+      </c>
+      <c r="CI7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CJ7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CK7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CL7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CM7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CN7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CO7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CP7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CQ7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CR7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CS7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CT7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CU7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CV7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CW7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="CX7" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+    </row>
+    <row r="8" spans="1:102" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1.1889205084349999</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1.1206959932585279</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1.0312764243475234</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1.0470144721784416</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1.0252111374343276</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1.0158825703078325</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0.99754043202865872</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.99615957883364437</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0.97685656321898762</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.96039856462072815</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0.96846207848766475</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.95498319542299226</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0.94337556574899339</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0.96744839262155014</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0.92769338530705725</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0.86727206296066028</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0.82472017699640998</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0.76894002397572891</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0.66380679626800254</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0.65305631166753941</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0.6871152299415384</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0.71859481887835241</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0.74790223711309056</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0.79091784715273028</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0.81121586681599944</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0.94913668647105376</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>1.0870575061261083</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>1.0964746257051343</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>1.0781097574837049</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>1.0409106501042227</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>1.0608518171660311</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>1.0807929842278394</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>1.0464763732622839</v>
+      </c>
+      <c r="AP8" s="3">
+        <v>0.99221859523491995</v>
+      </c>
+      <c r="AQ8" s="3">
+        <v>1.01501463678607</v>
+      </c>
+      <c r="AR8" s="3">
+        <v>1.0378106783372201</v>
+      </c>
+      <c r="AS8" s="3">
+        <v>1.06060671988837</v>
+      </c>
+      <c r="AT8" s="3">
+        <v>1.0057961170209109</v>
+      </c>
+      <c r="AU8" s="3">
+        <v>0.95098551415345178</v>
+      </c>
+      <c r="AV8" s="3">
+        <v>0.96222260153095573</v>
+      </c>
+      <c r="AW8" s="3">
+        <v>0.97345968890845957</v>
+      </c>
+      <c r="AX8" s="3">
+        <v>0.98469677628596364</v>
+      </c>
+      <c r="AY8" s="3">
+        <v>0.99037643241413353</v>
+      </c>
+      <c r="AZ8" s="3">
+        <v>0.99605608854230321</v>
+      </c>
+      <c r="BA8" s="3">
+        <v>0.98736234926232114</v>
+      </c>
+      <c r="BB8" s="3">
+        <v>0.97866860998233918</v>
+      </c>
+      <c r="BC8" s="3">
+        <v>0.96997487070235722</v>
+      </c>
+      <c r="BD8" s="3">
+        <v>0.96398692483800841</v>
+      </c>
+      <c r="BE8" s="3">
+        <v>0.9579989789736596</v>
+      </c>
+      <c r="BF8" s="3">
+        <v>0.95893696143103158</v>
+      </c>
+      <c r="BG8" s="3">
+        <v>0.95987494388840366</v>
+      </c>
+      <c r="BH8" s="3">
+        <v>0.96081292634577564</v>
+      </c>
+      <c r="BI8" s="3">
+        <v>0.93768707847620991</v>
+      </c>
+      <c r="BJ8" s="3">
+        <v>0.91456123060664429</v>
+      </c>
+      <c r="BK8" s="3">
+        <v>0.91099708676497237</v>
+      </c>
+      <c r="BL8" s="3">
+        <v>0.90743294292330057</v>
+      </c>
+      <c r="BM8" s="3">
+        <v>0.90386879908162854</v>
+      </c>
+      <c r="BN8" s="3">
+        <v>0.96274866013250016</v>
+      </c>
+      <c r="BO8" s="3">
+        <v>1.021628521183372</v>
+      </c>
+      <c r="BP8" s="3">
+        <v>1.014419014122248</v>
+      </c>
+      <c r="BQ8" s="3">
+        <v>1.007209507061124</v>
+      </c>
+      <c r="BR8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BT8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BU8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BZ8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CA8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CE8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CF8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CG8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CH8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CI8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CJ8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CK8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CM8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CO8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CP8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CQ8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CS8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CT8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CW8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CX8" s="3">
         <v>1</v>
       </c>
     </row>
